--- a/astro-site/public/dl/haccp-templates/15-health-inspection-checklist.xlsx
+++ b/astro-site/public/dl/haccp-templates/15-health-inspection-checklist.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="C6" s="29" t="inlineStr">
         <is>
-          <t>Hazard analysis, CCPs, critical limits, monitoring, corrective actions and verification (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)). Food Code §8-201.13 says when a written plan is required; UK: Reg. 852/2004, art. 5.</t>
+          <t>Hazard analysis, CCPs, critical limits, monitoring, corrective actions and verification, in template 12 (HACCP Plan). Food Code §8-201.13 says when a written plan is required; UK: Reg. 852/2004, art. 5.</t>
         </is>
       </c>
       <c r="D6" s="30" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>Proof of training for every food handler and the training log (BONUS-01 (Food Safety Training Log)). The person in charge must be a Certified Food Protection Manager (CFPM, Food Code §2-102.12), plus a food handler card where your state requires it. UK: no legal certificate; Level 2 is the usual standard.</t>
+          <t>Proof of training for every food handler and the training log in BONUS-01 (Food Safety Training Log). At least one supervisory employee must be a Certified Food Protection Manager (CFPM, §2-102.12(A)), plus a food handler card where your state requires it. UK: no legal certificate; Level 2 is the usual standard.</t>
         </is>
       </c>
       <c r="D8" s="30" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C9" s="29" t="inlineStr">
         <is>
-          <t>Available to any customer who asks, consistent with the allergen matrix (template 08 (Menu Allergen Matrix (US Big 9 &amp; UK 14))) and the current menu. US: the 9 major allergens, in writing (Food Code §3-602.12); UK: the 14 allergens.</t>
+          <t>Available to any customer who asks, consistent with the allergen matrix in template 08 (Menu Allergen Matrix) and the current menu. US: the 9 major allergens, in writing (Food Code §3-602.12); UK: the 14 allergens.</t>
         </is>
       </c>
       <c r="D9" s="30" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C10" s="29" t="inlineStr">
         <is>
-          <t>Contract in force, operator holding a state applicator license (UK: BPCA or NPTA member), a service report for every visit and the bait station map (template 07 (Pest Control Log &amp; Bait Station Map))</t>
+          <t>Contract in force, operator holding a state applicator license (UK: BPCA or NPTA member), a service report for every visit and the bait station map in template 07 (Pest Control Log &amp; Bait Station Map)</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C12" s="29" t="inlineStr">
         <is>
-          <t>On-site reading with the inspector's thermometer, checked against your template 01 (Food Temperature Log: Coolers, Freezers &amp; Hot Holding)</t>
+          <t>On-site reading with the inspector's thermometer, checked against your template 01 (Food Temperature Log)</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>Regular probe check in an ice bath or boiling water, with the deviation recorded (template 19 (Thermometer Calibration Log))</t>
+          <t>Regular probe check in an ice bath or boiling water, with the deviation recorded in template 19 (Thermometer Calibration Log)</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>Clean uniform, hair restraint, no jewelry (a plain ring band is allowed), closed-toe shoes, short nails and covered wounds</t>
+          <t>Clean uniform, hair restraint, no jewelry (a plain ring band is allowed), closed-toe shoes, trimmed fingernails (Pf, §2-302.11) and covered wounds</t>
         </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Priority foundation</t>
         </is>
       </c>
       <c r="E30" s="31" t="n"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C31" s="29" t="inlineStr">
         <is>
-          <t>Total polar materials (TPM) test, oil change log (template 09 (Fryer Oil Log (TPM Tests &amp; Disposal))) and a pickup receipt from a used-oil collector or recycler</t>
+          <t>Total polar materials (TPM) test, oil change log in template 09 (Fryer Oil Log) and a pickup receipt from a used-oil collector or recycler</t>
         </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C33" s="29" t="inlineStr">
         <is>
-          <t>Fish served raw, marinated or partly cooked: frozen at -4 °F for 168 hours or at -31 °F for 15 hours, with a log (template 18 (Parasite Destruction Log (Fish Served Raw))). UK/EU: 24 hours at -4 °F (-20 °C)</t>
+          <t>Fish served raw, marinated or partly cooked: frozen at -4 °F for 168 hours, at -31 °F for 15 hours, or at -31 °F until solid and then -4 °F for 24 hours, with a log in template 18 (Parasite Destruction Log). UK/EU: 24 hours at -4 °F (-20 °C)</t>
         </is>
       </c>
       <c r="D33" s="30" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>Trained staff, a written protocol and dedicated utensils when an allergy is declared (chart in template 14 (Allergen Chart &amp; Allergic Reaction Protocol))</t>
+          <t>Trained staff, a written protocol and dedicated utensils when an allergy is declared; chart in template 14 (Allergen Chart &amp; Allergic Reaction Protocol)</t>
         </is>
       </c>
       <c r="D34" s="30" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B48" s="36" t="inlineStr">
         <is>
-          <t>Check the temperatures of coolers, freezers and the steam table with a probe and enter them in template 01 (Food Temperature Log: Coolers, Freezers &amp; Hot Holding).</t>
+          <t>Check the temperatures of coolers, freezers and the steam table with a probe and enter them in template 01 (Food Temperature Log).</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="B56" s="36" t="inlineStr">
         <is>
-          <t>HACCP plan: hazard analysis (template 12 (HACCP Plan Template: Hazard Analysis &amp; CCPs)) and cleaning &amp; sanitizing schedule (template 03 (Master Cleaning &amp; Sanitizing Schedule)) with its list of chemicals.</t>
+          <t>HACCP plan: hazard analysis in template 12 (HACCP Plan) and cleaning &amp; sanitizing schedule in template 03 (Master Cleaning &amp; Sanitizing Schedule), with its list of chemicals.</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B57" s="36" t="inlineStr">
         <is>
-          <t>Temperature logs: daily (template 01 (Food Temperature Log: Coolers, Freezers &amp; Hot Holding)) and receiving (template 02 (Receiving Temperature Log)) for the past year.</t>
+          <t>Temperature logs for the past year: daily in template 01 (Food Temperature Log) and receiving in template 02 (Receiving Temperature Log).</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B58" s="36" t="inlineStr">
         <is>
-          <t>Receiving checklist (template 05 (Receiving Checklist for Deliveries)) together with its invoices / packing slips.</t>
+          <t>Receiving checklist in template 05 (Receiving Checklist for Deliveries), together with its invoices / packing slips.</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B59" s="36" t="inlineStr">
         <is>
-          <t>Traceability log for lots in and out (template 06 (Food Traceability Log (Lots In &amp; Out))).</t>
+          <t>Traceability log for lots in and out: template 06 (Food Traceability Log).</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B60" s="36" t="inlineStr">
         <is>
-          <t>Daily cleaning checklist and weekly tasks (template 04 (Daily Cleaning Checklist (AM/PM))).</t>
+          <t>Daily cleaning checklist and weekly tasks: template 04 (Daily Cleaning Checklist).</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B61" s="36" t="inlineStr">
         <is>
-          <t>Pest control: contract with the operator's license number, a service report for every visit and the bait station map (template 07 (Pest Control Log &amp; Bait Station Map)).</t>
+          <t>Pest control: contract with the operator's license number, a service report for every visit and the bait station map in template 07 (Pest Control Log &amp; Bait Station Map).</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B62" s="36" t="inlineStr">
         <is>
-          <t>Fryer oil log (template 09 (Fryer Oil Log (TPM Tests &amp; Disposal))) and used-oil pickup receipts.</t>
+          <t>Fryer oil log in template 09 (Fryer Oil Log) and used-oil pickup receipts.</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B63" s="36" t="inlineStr">
         <is>
-          <t>Water quality log (template 10 (Water Quality Log (Chlorine &amp; Private Supply))) and lab test reports if you have your own well or private water supply.</t>
+          <t>Water quality log in template 10 (Water Quality Log) and lab test reports if you have your own well or private water supply.</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B64" s="36" t="inlineStr">
         <is>
-          <t>Allergen matrix (template 08 (Menu Allergen Matrix (US Big 9 &amp; UK 14))) and the allergen guide available to customers.</t>
+          <t>Allergen matrix in template 08 (Menu Allergen Matrix) and the allergen guide available to customers.</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B65" s="36" t="inlineStr">
         <is>
-          <t>Cooking and reheating logs (template 16 (Cooking &amp; Reheating Temperature Log)), cooling and thawing logs (template 17 (Cooling &amp; Thawing Log (2-Stage Cooling))) and parasite destruction logs (template 18 (Parasite Destruction Log (Fish Served Raw))); keep the parasite destruction records for 90 days (§3-402.12).</t>
+          <t>Cooking and reheating logs in template 16 (Cooking &amp; Reheating Temperature Log), cooling and thawing logs in template 17 (Cooling &amp; Thawing Log) and parasite destruction logs in template 18 (Parasite Destruction Log); keep the parasite destruction records for 90 days (§3-402.12).</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B66" s="36" t="inlineStr">
         <is>
-          <t>Thermometer calibration log (template 19 (Thermometer Calibration Log)), corrective action log (template 11 (Corrective Action Log)) and staff training log (BONUS-01 (Food Safety Training Log)).</t>
+          <t>Thermometer calibration log in template 19 (Thermometer Calibration Log), corrective action log in template 11 (Corrective Action Log) and staff training log in BONUS-01 (Food Safety Training Log).</t>
         </is>
       </c>
     </row>
